--- a/excel/finland_universities_master.xlsx
+++ b/excel/finland_universities_master.xlsx
@@ -27,7 +27,7 @@
 
 <file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -115,7 +115,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aalto.fi/en/study-options</t>
+          <t xml:space="preserve">https://www.aalto.fi/en/admission-services/masters-admissions</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -125,27 +125,27 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t xml:space="preserve">University-wide international master's admissions</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Autumn</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Programme-specific</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Priority university for engineering and design</t>
+          <t xml:space="preserve">Main annual master's intake runs in December-January; applicants may apply to up to two study options.</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -177,7 +177,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.helsinki.fi/en/admissions-and-education</t>
+          <t xml:space="preserve">https://www.helsinki.fi/en/admissions-and-education/apply-bachelors-and-masters-programmes/apply-international-masters-programmes/how-apply</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -187,27 +187,27 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Autumn</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Programme-specific</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Priority university for research-intensive programs</t>
+          <t xml:space="preserve">Application period for autumn 2026 ran from 2026-01-02 to 2026-01-16.</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -239,7 +239,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.tuni.fi/en/study-with-us/apply-to-tampere-university</t>
+          <t xml:space="preserve">https://www.tuni.fi/en/study-with-us/apply-to-tampere-university/applying-to-university-masters-programmes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -249,27 +249,27 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t xml:space="preserve">University master's programmes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Autumn</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Possible scholarship and early-bird schemes</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add program-by-program deadlines</t>
+          <t xml:space="preserve">University-level master's admissions timeline for autumn 2026 is published centrally on TUNI.</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -301,7 +301,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.utu.fi/en/study-at-utu/apply</t>
+          <t xml:space="preserve">https://www.utu.fi/en/study-at-utu/apply-to-masters-programmes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -311,27 +311,27 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t xml:space="preserve">International master's degree programmes</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Autumn</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Programme-specific</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Add scholarship information</t>
+          <t xml:space="preserve">The next application round for autumn 2026 intake was 2026-01-07 to 2026-01-21 with attachments due 2026-01-28.</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -363,7 +363,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.oulu.fi/en/apply</t>
+          <t xml:space="preserve">https://www.oulu.fi/en/apply/how-apply/applying-masters-programmes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -373,30 +373,402 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme-specific</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu publishes a central deadlines page and a central application-documents page for master's admissions.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Finland</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lappeenranta</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT University</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.lut.fi/en</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.lut.fi/en/studies/apply-lut/applying-masters-programmes</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t xml:space="preserve">Autumn</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme-specific</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT uses separate Early Admission and Regular Admission windows depending on programme and applicant route.</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Finland</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joensuu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/how-to-apply</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master's programmes taught in English</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Add key departments and labs</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme-specific</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Most UEF English-taught master's programmes use the national first joint application round in January.</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Finland</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/study-with-us/masters-degree-programmes/how-to-apply-for-masters-programmes</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">English-taught master's degree programmes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme-specific</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JYU publishes a university-level timetable for all master's degree admissions each year.</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Finland</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vaasa</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/education/masters-programmes/how-apply</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">English-language master's programmes</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme-specific</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa offers both joint application and rolling admission routes for autumn 2026 depending on applicant background and programme.</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Finland</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/apply/application/masters-degree-studies-english</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master's degree studies in English</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme-specific</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken publishes separate Main Admission and Rolling Admission rounds for English master's programmes.</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Finland</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/study/apply/international-master-programmes/application-process/</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's degree programmes</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University-wide tuition fee scholarship scheme</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's programmes taught in English use the January national application period.</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -409,7 +781,7 @@
 
 <file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,37 +849,37 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t xml:space="preserve">University-wide international master's admissions</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-01</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-02</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Autumn</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aalto.fi/en/study-options</t>
+          <t xml:space="preserve">https://www.aalto.fi/en/admission-services/masters-admissions</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify exact annual application window</t>
+          <t xml:space="preserve">Document upload deadline 2026-01-09; results published 2026-04-08.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -529,37 +901,37 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-02</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-16</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Autumn</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.helsinki.fi/en/admissions-and-education</t>
+          <t xml:space="preserve">https://www.helsinki.fi/en/admissions-and-education/apply-bachelors-and-masters-programmes/apply-international-masters-programmes/how-apply</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify exact annual application window</t>
+          <t xml:space="preserve">Attachment deadline 2026-01-23; admissions results published between 2026-04-01 and 2026-04-15.</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -581,7 +953,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">University master's programmes</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -591,27 +963,27 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2025-12-15</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-01-05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-04-10</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.tuni.fi/en/study-with-us/apply-to-tampere-university</t>
+          <t xml:space="preserve">https://www.tuni.fi/en/study-with-us/apply-to-tampere-university/applying-to-university-masters-programmes</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify exact annual application window</t>
+          <t xml:space="preserve">Attachment deadline 2026-01-12; results on 2026-03-13; early-bird acceptance deadline 2026-03-27.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -633,37 +1005,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t xml:space="preserve">International master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-07</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-21</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Autumn</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.utu.fi/en/study-at-utu/apply</t>
+          <t xml:space="preserve">https://www.utu.fi/en/study-at-utu/apply-to-masters-programmes</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Verify exact annual application window</t>
+          <t xml:space="preserve">Attachment deadline 2026-01-28; results published 2026-03-26.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -685,40 +1057,456 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-07</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-21</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/apply/how-apply/applying-masters-programmes/deadlines</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attachment deadline 2026-01-28; graduating applicants submit final verified documents by 2026-07-31.</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT University</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regular Admission for master's studies</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">Autumn</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-15</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-21</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.lut.fi/en/studies/apply-lut/applying-masters-programmes/regular-admission-masters-studies</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supplementary document deadline 2026-01-28; results released by 2026-04-09.</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master's programmes taught in English</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-07</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-21</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/how-to-apply</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Required enclosures due 2026-01-28; verified educational documents due 2026-05-29 for completed degrees and 2026-07-30 for graduating applicants.</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">English-taught master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-07</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-21</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.oulu.fi/en/apply</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Verify exact annual application window</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/study-with-us/masters-degree-programmes/how-to-apply-for-masters-programmes</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attachment deadline 2026-01-28; applicants informed by 2026-04-01.</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joint application round</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-07</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-21</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/education/masters-programmes/how-apply</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling admission is also available for eligible applicants from 2025-10-01 until 2026-03-31.</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling admission</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-10-01</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-31</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/education/masters-programmes/how-apply</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling admission is open only to applicants with previous degrees from non-Finnish higher education institutions.</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main Admission round</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-07</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-21</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/apply/application/masters-degree-studies-english/main-admission-round/application-process-step-step</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attachment deadline 2026-01-28; all results published by 2026-05-27.</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling Admission round</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-12-08</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-04-15</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/index.php/en/apply/application/masters-degree-studies-english</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rolling Admission is limited to selected programmes and applicants with bachelor's degrees in economic sciences obtained outside Finland.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autumn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-07</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-01-21</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/study/apply/international-master-programmes/application-process/</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attachment deadline 2026-01-28; admission results sent in the beginning of April 2026.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -731,7 +1519,7 @@
 
 <file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,27 +1577,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">University-wide international master's admissions</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passport</t>
+          <t xml:space="preserve">Degree certificate</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">If graduated</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Upload with official translations when required.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aalto.fi/en/study-options</t>
+          <t xml:space="preserve">https://www.aalto.fi/en/admission-services/masters-admissions</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -831,12 +1619,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">University-wide international master's admissions</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transcript</t>
+          <t xml:space="preserve">Transcript of records</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -846,12 +1634,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Upload by 2026-01-09 if applying for autumn 2026 intake.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aalto.fi/en/study-options</t>
+          <t xml:space="preserve">https://www.aalto.fi/en/admission-services/masters-admissions</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -873,27 +1661,27 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">University-wide international master's admissions</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Motivation Letter</t>
+          <t xml:space="preserve">Proof of language proficiency</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Check Program</t>
+          <t xml:space="preserve">Yes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Program-specific requirement</t>
+          <t xml:space="preserve">Accepted methods are listed on Aalto language requirements page.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aalto.fi/en/study-options</t>
+          <t xml:space="preserve">https://www.aalto.fi/en/admission-services/language-requirements-in-masters-admissions</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -905,7 +1693,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">University of Helsinki</t>
+          <t xml:space="preserve">Aalto University</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -915,27 +1703,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">University-wide international master's admissions</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Passport</t>
+          <t xml:space="preserve">Study-option-specific documents</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yes</t>
+          <t xml:space="preserve">Check programme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Programme page may require GRE or GMAT or portfolio depending on field.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.helsinki.fi/en/admissions-and-education</t>
+          <t xml:space="preserve">https://www.aalto.fi/en/admission-services/masters-admissions</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -957,30 +1745,1920 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">International master's programmes</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transcript</t>
+          <t xml:space="preserve">Degree certificate</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t xml:space="preserve">If graduated</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Upload official educational documents in the application form.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/admissions-and-education/apply-bachelors-and-masters-programmes/apply-international-masters-programmes/how-apply</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcript of records</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Yes</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.helsinki.fi/en/admissions-and-education</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Final transcript required for all applicants; latest transcript if degree incomplete.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/admissions-and-education/apply-bachelors-and-masters-programmes/apply-international-masters-programmes/how-apply</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proof of language proficiency</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">English proficiency document required unless exempt.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/admissions-and-education/apply-bachelors-and-masters-programmes/application-attachments</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme-specific attachments</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check programme</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programmes may require motivation letter CV or other materials.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/admissions-and-education/apply-bachelors-and-masters-programmes/how-apply-to-international-masters-programmes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University master's programmes</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Degree certificate</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If graduated</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Completed-degree applicants must later submit officially certified documents by 2026-05-29.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/study-with-us/apply-to-tampere-university/applying-to-university-masters-programmes</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University master's programmes</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcript of records</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Latest transcript is accepted for unfinished degrees during the application phase.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/study-with-us/apply-to-tampere-university/applying-to-university-masters-programmes</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University master's programmes</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proof of language proficiency</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere requires proof of proficiency in the language of instruction.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/study-with-us/apply-to-tampere-university/applying-to-university-masters-programmes/faq-on-applying</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University master's programmes</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme-specific documents</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check programme</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme pages may require motivation letter CV portfolio or interview.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/study-with-us/apply-to-tampere-university/applying-to-university-masters-programmes</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Degree certificate</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If graduated</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Attach scans of original degree certificate and official translation if needed.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/study-at-utu/apply-to-masters-programmes</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcript of records</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Most recent transcript is accepted if the applicant has not yet graduated.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/study-at-utu/apply-to-masters-programmes</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proof of language skills</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Language proof options are listed on the UTU language requirements page referenced from the application guide.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/study-at-utu/apply-to-masters-programmes</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Passport or identity card</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Residence permit card also required if applying for fee exemption based on permit.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/study-at-utu/apply-to-masters-programmes</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme-specific documents</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check programme</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Examples include motivation letters self-introduction videos or other programme-specific materials.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/study-at-utu/apply-to-masters-programmes</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proof of language skills</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Language proof must be attached during the application period.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/apply/how-apply/documents</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcript of records</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Copy of transcript required for all applicants.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/apply/how-apply/documents</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Degree certificate</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If graduated</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Copy required if degree already completed.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/apply/how-apply/documents</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official translations</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If needed</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Required if original documents are not in Finnish Swedish or English.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/apply/how-apply/documents</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Passport or identity card</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Identification document must be attached to the application.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/apply/how-apply/documents</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's programmes</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme-specific attachments</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check programme</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Examples include motivation letter GMAT GRE CV ACT SAT or video depending on programme.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/apply/how-apply/documents</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT University</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regular Admission for master's studies</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Degree certificate</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If graduated</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Upload scan of the original bachelor's degree certificate and official translation when required.</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.lut.fi/en/studies/apply-lut/applying-masters-programmes/regular-admission-masters-studies/admission-criteria-software-engineering</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT University</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regular Admission for master's studies</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcript of records</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcript must include original study units cumulative units and grades.</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.lut.fi/en/studies/apply-lut/applying-masters-programmes/regular-admission-masters-studies/admission-criteria-software-engineering</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT University</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regular Admission for master's studies</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proof of English proficiency</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT accepts only listed test results or accepted degree-based proof methods.</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.lut.fi/en/studies/apply-lut/applying-masters-programmes/how-prove-your-proficiency-english</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT University</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Regular Admission for master's studies</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme-specific documents</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check programme</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admission criteria pages define additional programme-specific documents and evaluation material.</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.lut.fi/en/studies/apply-lut/applying-masters-programmes/regular-admission-masters-studies</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master's programmes taught in English</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Degree certificate</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If graduated</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Temporary degree certificates are accepted at application stage.</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/how-to-apply</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master's programmes taught in English</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcript of records</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Most recent transcript with translations must be uploaded by 2026-01-28 for foreign-degree applicants graduating later.</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/how-to-apply</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master's programmes taught in English</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official translations</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If needed</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Required when educational documents are not in English Finnish or Swedish.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/verification-of-official-educational-documents</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master's programmes taught in English</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proof of language proficiency</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Language proof must remain verifiable during the application period.</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/degree-programme/masters-degree-programme-in-english-language-and-culture</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">English-taught master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Admission criteria review</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Applicants must read the programme admission criteria before applying.</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/study-with-us/masters-degree-programmes/how-to-apply-for-masters-programmes</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">English-taught master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcript of records</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">For unfinished degrees applicants submit the transcript of completed studies to date.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/study-with-us/masters-degree-programmes/how-to-apply-for-masters-programmes</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">English-taught master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proof of language skills</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Language test or other accepted proof must be ready before the attachment deadline.</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/study-with-us/masters-degree-programmes/how-to-apply-for-masters-programmes</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">English-taught master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programme-specific attachments</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check programme</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GMAT GRE or other programme criteria may apply depending on the programme.</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/study-with-us/masters-degree-programmes/how-to-apply-for-masters-programmes</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joint application round</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Degree certificate</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If graduated</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High-quality scan of original degree certificate is required.</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/education/international-masters-programmes/application-process</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joint application round</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcript of records</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grading system explanation is mandatory if not clearly stated in the transcript.</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/education/international-masters-programmes/application-process</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joint application round</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official translations</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If needed</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Required for degree certificate and transcript if documents are not in English Finnish or Swedish.</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/education/international-masters-programmes/application-process</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joint application round</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proof of language proficiency</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accepted according to programme admissions criteria.</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/education/international-masters-programmes/application-process</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joint application round</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Passport or official ID</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Residence permit card copy also needed if applying for tuition fee exemption based on permit status.</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/education/international-masters-programmes/application-process</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main Admission round</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Degree certificate</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Diploma supplement is part of the requested educational documents when available.</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/apply/application/masters-degree-studies-english/attachments</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main Admission round</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcript of records</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official translations are required if documents are not in English Finnish or Swedish.</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/apply/application/masters-degree-studies-english/attachments</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main Admission round</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GPA or GMAT GRE report</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Check programme</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken requests GPA or GMAT or GRE documentation depending on programme and track.</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/apply/application/masters-degree-studies-english/attachments</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main Admission round</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Certificate of language proficiency</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Submit as high-quality scanned PDF.</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/apply/application/masters-degree-studies-english/attachments</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main Admission round</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CV in English</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conditional</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Required in main admission and for selected rolling-admission tracks.</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/apply/application/masters-degree-studies-english/attachments</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Main Admission round</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Passport or EU identity card</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Residence permit copy is needed where applicable.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/apply/application/masters-degree-studies-english/attachments</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Degree certificate</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If graduated</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Upload scans of original documents and translations if needed.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/study/apply/international-master-programmes/application-process/</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transcript of records</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">If still graduating state expected graduation date and upload studies completed so far.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/study/apply/international-master-programmes/application-process/</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Proof of language proficiency</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yes</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Applicants must meet university and programme-specific language requirements.</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/study/apply/international-master-programmes/</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Master</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">International master's degree programmes</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scholarship application</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Optional</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tuition-fee-paying applicants apply for scholarships through the application form where available.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/study/apply/international-master-programmes/application-process/</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -993,7 +3671,7 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1044,15 +3722,30 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t xml:space="preserve">citation_source</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citation_last_checked</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t xml:space="preserve">official_profile_url</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t xml:space="preserve">email</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">last_verified</t>
         </is>
@@ -1066,12 +3759,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Department Name</t>
+          <t xml:space="preserve">Department of Information and Communications Engineering</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor Name</t>
+          <t xml:space="preserve">Antti Oulasvirta</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1081,7 +3774,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research Area 1; Research Area 2</t>
+          <t xml:space="preserve">Human-computer interaction; User interfaces; Human factors; Interactive AI; Computational modeling</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1096,25 +3789,40 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">14763</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">63</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.aalto.fi/</t>
+          <t xml:space="preserve">Research.com profile summary</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.aalto.fi/en/people/antti-oulasvirta</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">antti.oulasvirta@aalto.fi</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aalto official profile does not expose ResearchGate or Google Scholar links directly on the page snapshot used here.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -1128,55 +3836,532 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Department Name</t>
+          <t xml:space="preserve">Department of Computer Science</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor Name</t>
+          <t xml:space="preserve">Jukka K Nurminen</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t xml:space="preserve">Professor of Computer Science</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Efficient software systems; Energy-efficient software; Mobile peer-to-peer systems; Cloud solutions</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://scholar.google.fi/citations?user=cmftgn4AAAAJ</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki research portal profile text</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://researchportal.helsinki.fi/en/persons/jukka-k-nurminen/</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jukka.k.nurminen@helsinki.fi</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google Scholar link is published directly on the university research portal profile.</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Computer Science</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hannu Toivonen</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Professor</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Research Area 1; Research Area 2</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artificial intelligence; Data science; Computational creativity; Data mining</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28000+</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60+</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki research group page</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/researchgroups/computational-creativity-and-data-mining/people/hannu-toivonen</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Citation count and h-index are stated on the official research group page as Google Scholar-based approximations.</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Research Centre of Gameful Realities</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Juho Hamari</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor of Gamification</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gamification; Game-based learning; Motivational systems; Extended reality; HCI</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.researchgate.net/profile/Juho-Hamari</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://scholar.google.com/citations?user=tKMlAegAAAAJ</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50000+</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.helsinki.fi/</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University research centre page; ResearchGate profile</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://research.tuni.fi/gameful-realities/gamification-group/</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juho.hamari@tuni.fi</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere research centre page states 50000+ citations and links both Google Scholar and ResearchGate.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information Systems Science</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jukka Heikkila</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information systems governance; Enterprise architecture; Business modelling</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.researchgate.net/profile/Jukka-Heikkilae</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://scholar.google.fi/citations?hl=en&amp;user=iLLaVWEAAAAJ&amp;view_op=list_works&amp;sortby=pubdate</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku staff profile</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/people/jukka-heikkila</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jups@utu.fi</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku profile publishes direct Google Scholar and ResearchGate links in profile text.</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Health Technology</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Antti Airola</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Associate Professor</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artificial intelligence; Data analytics; Machine learning; Health technology</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100+</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku staff profile biography</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/people/antti-airola</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ajairo@utu.fi</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The official profile states that he has co-authored over 100 peer-reviewed articles and links Google Scholar and ResearchGate profiles from the page.</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Information Technology and Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Harri Oinas-Kukkonen</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor and Dean</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information systems science; Computer-human interaction; Persuasive design; Digital interventions</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.researchgate.net/profile/Harri_Oinas-Kukkonen</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://scholar.google.fi/citations?hl=en&amp;oi=ao&amp;user=CBDr26wAAAAJ</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu researcher profile</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/researchers/harri-oinas-kukkonen</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harri.oinas-kukkonen@oulu.fi</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu profile exposes both Google Scholar and ResearchGate links directly.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biomimetics and Intelligent Systems Group</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heli Koskimaki</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adj. Prof.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machine learning; Data mining; Sensor fusion; Streaming data analysis; Wearable ICT</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu researcher profile</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/researchers/heli-koskimaki</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heli.koskimaki@oulu.fi</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official profile confirms both Google Scholar and ResearchGate profile links but their exact public URLs were not fetched automatically here.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>

--- a/excel/finland_universities_master.xlsx
+++ b/excel/finland_universities_master.xlsx
@@ -3671,7 +3671,7 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4367,6 +4367,1161 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT University</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Engineering Science</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heikki Kalviainen</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer vision; Pattern recognition; Machine learning; AI engineering</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT official profile</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.lut.fi/en/profiles/heikki-kalviainen</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT official profile was used for role and research focus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT University</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Engineering Science</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lasse Lensu</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer vision; Pattern recognition; Image analysis; Machine learning</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT official profile</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.lut.fi/en/profiles/lasse-lensu</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT official profile was used for role and research focus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT University</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Engineering Science</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zhisong Liu</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Associate Professor</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Industrial AI; Machine learning; Computer vision; Autonomous systems</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13235</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT official profile</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.lut.fi/en/profiles/zhisong-liu</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official LUT profile states 13235 citations and h-index 48.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Computing</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pauli Miettinen</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data mining; Machine learning; Discrete optimization; Pattern discovery</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UEF official profile</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/person/pauli.miettinen</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UEF official profile used for role and research fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Computing</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Markku Tukiainen</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Human-computer interaction; Learning technologies; Computer science education</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UEF official profile</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/person/markku.tukiainen</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UEF official profile used for role and research fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Computing</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ville Hautamaki</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Speech processing; Speaker recognition; Biometrics; Audio analysis</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UEF official profile</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/person/ville.hautamaki</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UEF official profile used for role and research fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Information Technology</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Michael Emmerich</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Multi-objective optimization; Bayesian optimization; Data science; Simulation</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JYU official profile</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/people/michael-emmerich</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JYU official profile used for title and research topics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Information Technology</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vagan Terziyan</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artificial intelligence; Semantic web; Knowledge engineering; Trust systems</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JYU official profile</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/people/vagan-terziyan</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JYU official profile used for title and research topics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Technology and Innovations</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tero Vartiainen</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information systems; Digital transformation; Human-computer interaction; Organizational communication</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa official profile</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/person/tero-vartiainen</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa official profile used for title and research description.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Management</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Harri Jalonen</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Knowledge management; Artificial intelligence in organizations; Social robotics; Futures studies</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa official profile</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/person/harri-jalonen</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa official profile used for title and research description.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Management and Organisation</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denise Salin</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Management and organisation; Workplace bullying; Leadership; Gender and diversity</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4296</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken official profile</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/person/denise-salin</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official Hanken profile states citation and h-index figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Marketing</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kaj Storbacka</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Markets and strategy; Sales management; Business model innovation; Customer relationships</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken official profile</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/person/kaj-storbacka</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken official profile used for title and research focus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Economics</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joacim Tag</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assistant Professor</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Economics; Applied econometrics; Productivity; Labor markets</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">750</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken official profile</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/person/joacim-tag</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official Hanken profile states citation and h-index figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer Science</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ivan Porres</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software engineering; Distributed systems; Formal methods; Process modeling</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi official profile</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/people/ivan-porres/</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi official profile used for title and research focus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer Science</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Johan Lilius</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Embedded systems; Dependable systems; Software engineering; Computer architecture</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi official profile</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/people/johan-lilius/</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi official profile used for title and research focus.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/excel/finland_universities_master.xlsx
+++ b/excel/finland_universities_master.xlsx
@@ -20,7 +20,8 @@
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
     <sheet name="Deadlines" sheetId="2" r:id="rId2"/>
     <sheet name="Documents" sheetId="3" r:id="rId3"/>
-    <sheet name="Professors" sheetId="4" r:id="rId4"/>
+    <sheet name="Departments" sheetId="4" r:id="rId4"/>
+    <sheet name="Professors" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -3671,7 +3672,7 @@
 
 <file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:I136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3682,70 +3683,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t xml:space="preserve">department_name</t>
+          <t xml:space="preserve">unit_type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t xml:space="preserve">professor_name</t>
+          <t xml:space="preserve">unit_name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t xml:space="preserve">title</t>
+          <t xml:space="preserve">parent_unit</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t xml:space="preserve">research_areas</t>
+          <t xml:space="preserve">campus_or_city</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">researchgate_url</t>
+          <t xml:space="preserve">focus_areas</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t xml:space="preserve">google_scholar_url</t>
+          <t xml:space="preserve">official_url</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t xml:space="preserve">citation_count</t>
+          <t xml:space="preserve">notes</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">h_index</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">citation_source</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">citation_last_checked</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">official_profile_url</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">email</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">notes</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
         <is>
           <t xml:space="preserve">last_verified</t>
         </is>
@@ -3759,70 +3730,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Department of Information and Communications Engineering</t>
+          <t xml:space="preserve">School</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antti Oulasvirta</t>
+          <t xml:space="preserve">School of Arts, Design and Architecture</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Human-computer interaction; User interfaces; Human factors; Interactive AI; Computational modeling</t>
+          <t xml:space="preserve">Espoo</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Art; Design; Architecture; Media</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.aalto.fi/en/school-of-arts-design-and-architecture</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">14763</t>
+          <t xml:space="preserve">Official Aalto school page.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Research.com profile summary</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.aalto.fi/en/people/antti-oulasvirta</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">antti.oulasvirta@aalto.fi</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aalto official profile does not expose ResearchGate or Google Scholar links directly on the page snapshot used here.</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -3831,75 +3772,45 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">University of Helsinki</t>
+          <t xml:space="preserve">Aalto University</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Department of Computer Science</t>
+          <t xml:space="preserve">Department</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jukka K Nurminen</t>
+          <t xml:space="preserve">Department of Architecture</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor of Computer Science</t>
+          <t xml:space="preserve">School of Arts, Design and Architecture</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Efficient software systems; Energy-efficient software; Mobile peer-to-peer systems; Cloud solutions</t>
+          <t xml:space="preserve">Espoo</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Architecture</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://scholar.google.fi/citations?user=cmftgn4AAAAJ</t>
+          <t xml:space="preserve">https://www.aalto.fi/en/department-of-architecture</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Official Aalto department page.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">University of Helsinki research portal profile text</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://researchportal.helsinki.fi/en/persons/jukka-k-nurminen/</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jukka.k.nurminen@helsinki.fi</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Google Scholar link is published directly on the university research portal profile.</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -3908,75 +3819,45 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">University of Helsinki</t>
+          <t xml:space="preserve">Aalto University</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Department of Computer Science</t>
+          <t xml:space="preserve">Department</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hannu Toivonen</t>
+          <t xml:space="preserve">Department of Art and Media</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor</t>
+          <t xml:space="preserve">School of Arts, Design and Architecture</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artificial intelligence; Data science; Computational creativity; Data mining</t>
+          <t xml:space="preserve">Espoo</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Art; Media; Visual culture</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.aalto.fi/en/department-of-art-and-media</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">28000+</t>
+          <t xml:space="preserve">Official Aalto department page.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60+</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">University of Helsinki research group page</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.helsinki.fi/en/researchgroups/computational-creativity-and-data-mining/people/hannu-toivonen</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Citation count and h-index are stated on the official research group page as Google Scholar-based approximations.</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -3985,75 +3866,45 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tampere University</t>
+          <t xml:space="preserve">Aalto University</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research Centre of Gameful Realities</t>
+          <t xml:space="preserve">Department</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Juho Hamari</t>
+          <t xml:space="preserve">Department of Design</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor of Gamification</t>
+          <t xml:space="preserve">School of Arts, Design and Architecture</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gamification; Game-based learning; Motivational systems; Extended reality; HCI</t>
+          <t xml:space="preserve">Espoo</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.researchgate.net/profile/Juho-Hamari</t>
+          <t xml:space="preserve">Design</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://scholar.google.com/citations?user=tKMlAegAAAAJ</t>
+          <t xml:space="preserve">https://www.aalto.fi/en/department-of-design</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">50000+</t>
+          <t xml:space="preserve">Official Aalto department page.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tampere University research centre page; ResearchGate profile</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://research.tuni.fi/gameful-realities/gamification-group/</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">juho.hamari@tuni.fi</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tampere research centre page states 50000+ citations and links both Google Scholar and ResearchGate.</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -4062,75 +3913,45 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">University of Turku</t>
+          <t xml:space="preserve">Aalto University</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Information Systems Science</t>
+          <t xml:space="preserve">Department</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jukka Heikkila</t>
+          <t xml:space="preserve">Department of Film</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor</t>
+          <t xml:space="preserve">School of Arts, Design and Architecture</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Information systems governance; Enterprise architecture; Business modelling</t>
+          <t xml:space="preserve">Espoo</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.researchgate.net/profile/Jukka-Heikkilae</t>
+          <t xml:space="preserve">Film; Television; Scenography</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://scholar.google.fi/citations?hl=en&amp;user=iLLaVWEAAAAJ&amp;view_op=list_works&amp;sortby=pubdate</t>
+          <t xml:space="preserve">https://www.aalto.fi/en/department-of-film</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Official Aalto department page.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">University of Turku staff profile</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.utu.fi/en/people/jukka-heikkila</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">jups@utu.fi</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">University of Turku profile publishes direct Google Scholar and ResearchGate links in profile text.</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -4139,75 +3960,45 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">University of Turku</t>
+          <t xml:space="preserve">Aalto University</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health Technology</t>
+          <t xml:space="preserve">School</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antti Airola</t>
+          <t xml:space="preserve">School of Business</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Associate Professor</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artificial intelligence; Data analytics; Machine learning; Health technology</t>
+          <t xml:space="preserve">Espoo</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Business; Economics; Management</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.aalto.fi/en/school-of-business</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">100+</t>
+          <t xml:space="preserve">Official Aalto school page.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">University of Turku staff profile biography</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.utu.fi/en/people/antti-airola</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ajairo@utu.fi</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">The official profile states that he has co-authored over 100 peer-reviewed articles and links Google Scholar and ResearchGate profiles from the page.</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -4216,75 +4007,45 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">University of Oulu</t>
+          <t xml:space="preserve">Aalto University</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Faculty of Information Technology and Electrical Engineering</t>
+          <t xml:space="preserve">Department</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harri Oinas-Kukkonen</t>
+          <t xml:space="preserve">Department of Accounting and Business Law</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor and Dean</t>
+          <t xml:space="preserve">School of Business</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Information systems science; Computer-human interaction; Persuasive design; Digital interventions</t>
+          <t xml:space="preserve">Espoo</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://www.researchgate.net/profile/Harri_Oinas-Kukkonen</t>
+          <t xml:space="preserve">Accounting; Business law</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://scholar.google.fi/citations?hl=en&amp;oi=ao&amp;user=CBDr26wAAAAJ</t>
+          <t xml:space="preserve">https://www.aalto.fi/en/department-of-accounting-and-business-law</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Official Aalto department page.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">University of Oulu researcher profile</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.oulu.fi/en/researchers/harri-oinas-kukkonen</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">harri.oinas-kukkonen@oulu.fi</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">University of Oulu profile exposes both Google Scholar and ResearchGate links directly.</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -4293,75 +4054,45 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">University of Oulu</t>
+          <t xml:space="preserve">Aalto University</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biomimetics and Intelligent Systems Group</t>
+          <t xml:space="preserve">Department</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heli Koskimaki</t>
+          <t xml:space="preserve">Department of Economics</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Adj. Prof.</t>
+          <t xml:space="preserve">School of Business</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Machine learning; Data mining; Sensor fusion; Streaming data analysis; Wearable ICT</t>
+          <t xml:space="preserve">Espoo</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Economics</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.aalto.fi/en/department-of-economics</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Official Aalto department page.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">University of Oulu researcher profile</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.oulu.fi/en/researchers/heli-koskimaki</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">heli.koskimaki@oulu.fi</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Official profile confirms both Google Scholar and ResearchGate profile links but their exact public URLs were not fetched automatically here.</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-03-14</t>
         </is>
@@ -4370,1153 +4101,8133 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUT University</t>
+          <t xml:space="preserve">Aalto University</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">School of Engineering Science</t>
+          <t xml:space="preserve">Department</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heikki Kalviainen</t>
+          <t xml:space="preserve">Department of Finance</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor</t>
+          <t xml:space="preserve">School of Business</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computer vision; Pattern recognition; Machine learning; AI engineering</t>
+          <t xml:space="preserve">Espoo</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Finance</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.aalto.fi/en/department-of-finance</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Official Aalto department page.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LUT official profile</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.lut.fi/en/profiles/heikki-kalviainen</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LUT official profile was used for role and research focus.</t>
+          <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUT University</t>
+          <t xml:space="preserve">Aalto University</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">School of Engineering Science</t>
+          <t xml:space="preserve">Department</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lasse Lensu</t>
+          <t xml:space="preserve">Department of Information and Service Management</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor</t>
+          <t xml:space="preserve">School of Business</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computer vision; Pattern recognition; Image analysis; Machine learning</t>
+          <t xml:space="preserve">Espoo</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Information systems; Service management</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.aalto.fi/en/department-of-information-and-service-management</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Official Aalto department page.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LUT official profile</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.lut.fi/en/profiles/lasse-lensu</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LUT official profile was used for role and research focus.</t>
+          <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">LUT University</t>
+          <t xml:space="preserve">Aalto University</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">School of Engineering Science</t>
+          <t xml:space="preserve">Department</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zhisong Liu</t>
+          <t xml:space="preserve">Department of Management Studies</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Associate Professor</t>
+          <t xml:space="preserve">School of Business</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Industrial AI; Machine learning; Computer vision; Autonomous systems</t>
+          <t xml:space="preserve">Espoo</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Management; Organization</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.aalto.fi/en/department-of-management-studies</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">13235</t>
+          <t xml:space="preserve">Official Aalto department page.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t xml:space="preserve">48</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LUT official profile</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.lut.fi/en/profiles/zhisong-liu</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Official LUT profile states 13235 citations and h-index 48.</t>
+          <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">University of Eastern Finland</t>
+          <t xml:space="preserve">Aalto University</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">School of Computing</t>
+          <t xml:space="preserve">Department</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pauli Miettinen</t>
+          <t xml:space="preserve">Department of Marketing</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor</t>
+          <t xml:space="preserve">School of Business</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Data mining; Machine learning; Discrete optimization; Pattern discovery</t>
+          <t xml:space="preserve">Espoo</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Marketing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.aalto.fi/en/department-of-marketing</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Official Aalto department page.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UEF official profile</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.uef.fi/en/person/pauli.miettinen</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UEF official profile used for role and research fields.</t>
+          <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">University of Eastern Finland</t>
+          <t xml:space="preserve">Aalto University</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">School of Computing</t>
+          <t xml:space="preserve">School</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Markku Tukiainen</t>
+          <t xml:space="preserve">School of Chemical Engineering</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Human-computer interaction; Learning technologies; Computer science education</t>
+          <t xml:space="preserve">Espoo</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Chemical engineering; Materials; Bioproducts</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.aalto.fi/en/school-of-chemical-engineering</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Official Aalto school page.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UEF official profile</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.uef.fi/en/person/markku.tukiainen</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UEF official profile used for role and research fields.</t>
+          <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">University of Eastern Finland</t>
+          <t xml:space="preserve">Aalto University</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">School of Computing</t>
+          <t xml:space="preserve">Department</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ville Hautamaki</t>
+          <t xml:space="preserve">Department of Bioproducts and Biosystems</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor</t>
+          <t xml:space="preserve">School of Chemical Engineering</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Speech processing; Speaker recognition; Biometrics; Audio analysis</t>
+          <t xml:space="preserve">Espoo</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Bioproducts; Biosystems</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.aalto.fi/en/department-of-bioproducts-and-biosystems</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Official Aalto department page.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UEF official profile</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.uef.fi/en/person/ville.hautamaki</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">UEF official profile used for role and research fields.</t>
+          <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">University of Jyvaskyla</t>
+          <t xml:space="preserve">Aalto University</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Faculty of Information Technology</t>
+          <t xml:space="preserve">Department</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Michael Emmerich</t>
+          <t xml:space="preserve">Department of Chemistry and Materials Science</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor</t>
+          <t xml:space="preserve">School of Chemical Engineering</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Multi-objective optimization; Bayesian optimization; Data science; Simulation</t>
+          <t xml:space="preserve">Espoo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Chemistry; Materials science</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.aalto.fi/en/department-of-chemistry-and-materials-science</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Official Aalto department page.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JYU official profile</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.jyu.fi/en/people/michael-emmerich</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JYU official profile used for title and research topics.</t>
+          <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">University of Jyvaskyla</t>
+          <t xml:space="preserve">Aalto University</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Faculty of Information Technology</t>
+          <t xml:space="preserve">Department</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vagan Terziyan</t>
+          <t xml:space="preserve">Department of Chemical and Metallurgical Engineering</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor</t>
+          <t xml:space="preserve">School of Chemical Engineering</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artificial intelligence; Semantic web; Knowledge engineering; Trust systems</t>
+          <t xml:space="preserve">Espoo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Chemical engineering; Metallurgy</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.aalto.fi/en/department-of-chemical-and-metallurgical-engineering</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Official Aalto department page.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JYU official profile</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.jyu.fi/en/people/vagan-terziyan</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">JYU official profile used for title and research topics.</t>
+          <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">University of Vaasa</t>
+          <t xml:space="preserve">Aalto University</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">School of Technology and Innovations</t>
+          <t xml:space="preserve">School</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tero Vartiainen</t>
+          <t xml:space="preserve">School of Electrical Engineering</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Information systems; Digital transformation; Human-computer interaction; Organizational communication</t>
+          <t xml:space="preserve">Espoo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Electrical engineering; Electronics; Automation</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.aalto.fi/en/school-of-electrical-engineering</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Official Aalto school page.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">University of Vaasa official profile</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.uwasa.fi/en/person/tero-vartiainen</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">University of Vaasa official profile used for title and research description.</t>
+          <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">University of Vaasa</t>
+          <t xml:space="preserve">Aalto University</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">School of Management</t>
+          <t xml:space="preserve">School</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Harri Jalonen</t>
+          <t xml:space="preserve">School of Engineering</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Knowledge management; Artificial intelligence in organizations; Social robotics; Futures studies</t>
+          <t xml:space="preserve">Espoo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Engineering; Built environment; Energy</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.aalto.fi/en/school-of-engineering</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Official Aalto school page.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">University of Vaasa official profile</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.uwasa.fi/en/person/harri-jalonen</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">University of Vaasa official profile used for title and research description.</t>
+          <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hanken School of Economics</t>
+          <t xml:space="preserve">Aalto University</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Department of Management and Organisation</t>
+          <t xml:space="preserve">Department</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Denise Salin</t>
+          <t xml:space="preserve">Department of Built Environment</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor</t>
+          <t xml:space="preserve">School of Engineering</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Management and organisation; Workplace bullying; Leadership; Gender and diversity</t>
+          <t xml:space="preserve">Espoo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Built environment; Real estate; Water</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.aalto.fi/en/department-of-built-environment</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">4296</t>
+          <t xml:space="preserve">Official Aalto department page.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t xml:space="preserve">31</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hanken official profile</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.hanken.fi/en/person/denise-salin</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Official Hanken profile states citation and h-index figures.</t>
+          <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hanken School of Economics</t>
+          <t xml:space="preserve">Aalto University</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Department of Marketing</t>
+          <t xml:space="preserve">Department</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kaj Storbacka</t>
+          <t xml:space="preserve">Department of Civil Engineering</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor</t>
+          <t xml:space="preserve">School of Engineering</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Markets and strategy; Sales management; Business model innovation; Customer relationships</t>
+          <t xml:space="preserve">Espoo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Civil engineering</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.aalto.fi/en/department-of-civil-engineering</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Official Aalto department page.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hanken official profile</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.hanken.fi/en/person/kaj-storbacka</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hanken official profile used for title and research focus.</t>
+          <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hanken School of Economics</t>
+          <t xml:space="preserve">Aalto University</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Department of Economics</t>
+          <t xml:space="preserve">Department</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Joacim Tag</t>
+          <t xml:space="preserve">Department of Energy and Mechanical Engineering</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assistant Professor</t>
+          <t xml:space="preserve">School of Engineering</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Economics; Applied econometrics; Productivity; Labor markets</t>
+          <t xml:space="preserve">Espoo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Energy; Mechanical engineering</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.aalto.fi/en/department-of-energy-and-mechanical-engineering</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">750</t>
+          <t xml:space="preserve">Official Aalto department page.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hanken official profile</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.hanken.fi/en/person/joacim-tag</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Official Hanken profile states citation and h-index figures.</t>
+          <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Abo Akademi University</t>
+          <t xml:space="preserve">Aalto University</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computer Science</t>
+          <t xml:space="preserve">School</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ivan Porres</t>
+          <t xml:space="preserve">School of Science</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Professor</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Software engineering; Distributed systems; Formal methods; Process modeling</t>
+          <t xml:space="preserve">Espoo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Computer science; Mathematics; Physics; Industrial engineering</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">https://www.aalto.fi/en/school-of-science</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Official Aalto school page.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Abo Akademi official profile</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://www.abo.fi/en/people/ivan-porres/</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Abo Akademi official profile used for title and research focus.</t>
+          <t xml:space="preserve">2026-03-14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Aalto University</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Applied Physics</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Science</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Espoo</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Applied physics</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.aalto.fi/en/department-of-applied-physics</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official Aalto department page.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aalto University</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Computer Science</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Science</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Espoo</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer science</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.aalto.fi/en/department-of-computer-science</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official Aalto department page.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aalto University</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Industrial Engineering and Management</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Science</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Espoo</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Industrial engineering; Management</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.aalto.fi/en/department-of-industrial-engineering-and-management</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official Aalto department page.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aalto University</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Mathematics and Systems Analysis</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Science</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Espoo</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mathematics; Systems analysis</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.aalto.fi/en/department-of-mathematics-and-systems-analysis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official Aalto department page.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aalto University</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Neuroscience and Biomedical Engineering</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Science</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Espoo</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Neuroscience; Biomedical engineering</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.aalto.fi/en/department-of-neuroscience-and-biomedical-engineering</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official Aalto department page.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Agriculture and Forestry</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Agriculture; Forestry; Food sciences</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-agriculture-and-forestry</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university faculty page.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Arts</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arts</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-arts</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university faculty page.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Biological and Environmental Sciences</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biology; Environmental sciences</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-biological-and-environmental-sciences</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university faculty page.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Environmental Sciences</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Biological and Environmental Sciences</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Environmental sciences</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-biological-and-environmental-sciences</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department listed on official faculty organization page.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Educational Sciences</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-educational-sciences</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university faculty page.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Law</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Law</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-law</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university faculty page.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Medicine</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medicine</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-medicine</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university faculty page.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Pharmacy</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pharmacy</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-pharmacy</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university faculty page.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer science; Physics; Mathematics; Chemistry</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-science</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university faculty page.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Computer Science</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer science</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-science/faculty/department-computer-science</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official department page.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Physics</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physics</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-science/faculty/department-physics</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official department page.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Chemistry</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemistry</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-science/faculty/department-chemistry</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official department page.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Geosciences and Geography</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Geosciences; Geography</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-science/faculty/department-geosciences-and-geography</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official department page.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Mathematics and Statistics</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mathematics; Statistics</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-science/faculty/department-mathematics-and-statistics</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official department page.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Social Sciences</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Social sciences</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-social-sciences</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university faculty page.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Theology</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Theology</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-theology</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university faculty page.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Veterinary Medicine</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Veterinary medicine</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/faculties/faculty-veterinary-medicine</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university faculty page.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Built Environment</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Architecture; Civil engineering; Built environment</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Education and Culture</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education; Humanities; Languages</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Information Technology and Communication Sciences</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computing; Media; Information studies</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Engineering and Natural Sciences</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engineering; Natural sciences</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Management and Business</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Management; Economics; Administrative sciences</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Medicine and Health Technology</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medicine; Health technology</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Social Sciences</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Social sciences; Psychology; Health sciences</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">History, Philosophy and Literary Studies</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Social Sciences</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">History; Philosophy; Literature</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties-and-units/faculty-social-sciences</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculty unit list.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Social Research</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Social Sciences</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Social research</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties-and-units/faculty-social-sciences</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculty unit list.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Welfare Sciences</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Social Sciences</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Social work; Welfare</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties-and-units/faculty-social-sciences</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculty unit list.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Health Sciences</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Social Sciences</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Health sciences</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties-and-units/faculty-social-sciences</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculty unit list.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automation Technology and Mechanical Engineering</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Engineering and Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automation; Mechanical engineering</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties-and-units/faculty-engineering-and-natural-sciences</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculty unit list.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Materials Science and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Engineering and Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Materials science; Environmental engineering</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties-and-units/faculty-engineering-and-natural-sciences</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculty unit list.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physics</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Engineering and Natural Sciences</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physics</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.tuni.fi/en/about-us/faculties-and-units/faculty-engineering-and-natural-sciences</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculty unit list.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Education</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Humanities</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanities</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Law</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Law</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Medicine</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medicine</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science; Data science; Mathematics; Physics</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Biology</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biology</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties/faculty-of-science</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biodiversity Unit</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biodiversity</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties/faculty-of-science</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Chemistry</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemistry</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties/faculty-of-science</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Computing</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computing</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties/faculty-of-science</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Geography and Geology</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Geography; Geology</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties/faculty-of-science</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Learning Analytics</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Learning analytics</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties/faculty-of-science</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Mathematics and Statistics</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mathematics; Statistics</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties/faculty-of-science</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Physics and Astronomy</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physics; Astronomy</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties/faculty-of-science</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku School of Economics</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Economics; Business</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Social Sciences</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Social sciences</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Technology</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Engineering; Computing; Biotechnology</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Computing</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Technology</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computing</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties/faculty-of-technology</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Biotechnology</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Technology</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biotechnology</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties/faculty-of-technology</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Mechanical and Materials Engineering</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Technology</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mechanical engineering; Materials engineering</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/university/faculties/faculty-of-technology</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Biochemistry and Molecular Medicine</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biochemistry; Molecular medicine</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/university/faculties-and-units</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties and units page.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Education and Psychology</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education; Psychology</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/university/faculties-and-units</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties and units page.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Humanities</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanities</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/university/faculties-and-units</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties and units page.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Information Technology and Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information technology; Electrical engineering</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/university/faculties-and-units</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties and units page.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Centre for Wireless Communications</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Information Technology and Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wireless communications; 6G</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/research/research-units/centre-wireless-communications</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official research unit page.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Information Technology and Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer science; Engineering</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/research/research-units/computer-science-and-engineering</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official research unit page.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Microelectronics Research Unit</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Information Technology and Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Microelectronics</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/research/research-units/microelectronics-research-unit</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official research unit page.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Medicine</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medicine</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/university/faculties-and-units</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties and units page.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/university/faculties-and-units</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties and units page.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu Business School</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/university/faculties-and-units</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties and units page.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu Mining School</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mining</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/university/faculties-and-units</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties and units page.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Technology</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technology</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/university/faculties-and-units</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties and units page.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Industrial Engineering and Management</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Technology</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Industrial engineering; Management</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/research/research-units/industrial-engineering-and-management</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official research unit page.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Water, Energy and Environmental Engineering</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Technology</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oulu</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Water; Energy; Environmental engineering</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/research/research-units/water-energy-and-environmental-engineering</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official research unit page.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT University</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT School of Engineering Science</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lappeenranta</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software engineering; Industrial engineering; Data science</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.lut.fi/en/about-us/lut-schools/lut-school-engineering-science</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official LUT school page.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT University</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT School of Energy Systems</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lappeenranta</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Energy; Mechanical engineering; Electrical engineering</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.lut.fi/en/about-us/lut-schools/lut-school-energy-systems</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official LUT school page.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT University</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT Business School</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lappeenranta</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business; Management; Economics</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.lut.fi/en/about-us/lut-schools/lut-business-school</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official LUT school page.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophical Faculty</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joensuu</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education; Humanities; Theology</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/organisation</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official organisation page.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science, Forestry and Technology</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joensuu</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science; Forestry; Technology</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/organisation</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official organisation page.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Computing</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science, Forestry and Technology</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joensuu</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computing</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/organisation</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official organisation page.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Forest Sciences</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science, Forestry and Technology</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joensuu</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forest sciences</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/organisation</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official organisation page.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Pharmacy</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science, Forestry and Technology</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kuopio</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pharmacy</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/organisation</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official organisation page.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Applied Educational Science and Teacher Education</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philosophical Faculty</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joensuu</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Teacher education</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/organisation</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official organisation page.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Health Sciences</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kuopio</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Medicine; Public health; Nursing</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/organisation</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official organisation page.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Social Sciences and Business Studies</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kuopio</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business; Law; Social sciences</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/organisation</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official organisation page.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Education and Psychology</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education; Psychology</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/education/faculties</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Humanities and Social Sciences</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Humanities; Social sciences</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/education/faculties</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of History and Ethnology</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Humanities and Social Sciences</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">History; Ethnology</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/education/faculties/faculty-of-humanities-and-social-sciences</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Language and Communication Studies</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Humanities and Social Sciences</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Languages; Communication</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/education/faculties/faculty-of-humanities-and-social-sciences</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Music, Art and Culture Studies</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Humanities and Social Sciences</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Music; Art; Culture</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/education/faculties/faculty-of-humanities-and-social-sciences</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Social Sciences and Philosophy</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Humanities and Social Sciences</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Social sciences; Philosophy</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/education/faculties/faculty-of-humanities-and-social-sciences</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Information Technology</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information systems; Software engineering; Data science</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/education/faculties/faculty-of-information-technology</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculty page.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information Systems Science</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Information Technology</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information systems</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/education/faculties/faculty-of-information-technology</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software Engineering</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Information Technology</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software engineering</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/education/faculties/faculty-of-information-technology</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Learning and Cognitive Systems</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Information Technology</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Learning systems; Cognitive systems</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/education/faculties/faculty-of-information-technology</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unit</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computational Sciences</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Information Technology</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computational sciences; Data science</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/education/faculties/faculty-of-information-technology</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Mathematics and Science</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mathematics; Science</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/education/faculties</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Biological and Environmental Science</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Mathematics and Science</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biology; Environmental science</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/education/faculties/faculty-of-mathematics-and-science</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Chemistry</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Mathematics and Science</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chemistry</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/education/faculties/faculty-of-mathematics-and-science</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Physics</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Mathematics and Science</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Physics</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/education/faculties/faculty-of-mathematics-and-science</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Mathematics and Statistics</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Mathematics and Science</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mathematics; Statistics</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/education/faculties/faculty-of-mathematics-and-science</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Listed on official faculty page.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Business and Economics</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business; Economics</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/education/faculties</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Sport and Health Sciences</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sport sciences; Health sciences</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/education/faculties</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official faculties page.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Accounting and Finance</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vaasa</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accounting; Finance</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/about/organization</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official organization page.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Management</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vaasa</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Management; Public management</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/about/organization</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official organization page.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Marketing and Communication</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vaasa</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marketing; Communication</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/about/organization</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official organization page.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Technology and Innovations</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vaasa</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Technology; Information systems; Industrial management</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/about/organization</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official organization page.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Accounting and Commercial Law</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Accounting; Commercial law</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/departments-and-centres</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official departments and centres page.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Economics</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Economics; Statistics</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/departments-and-centres</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official departments and centres page.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Management and Organisation</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Management; Organisation; Information systems science</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/departments-and-centres</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official departments and centres page.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Marketing</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Helsinki</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marketing; Supply chain management; Social responsibility</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/departments-and-centres</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official departments and centres page.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
           <t xml:space="preserve">Abo Akademi University</t>
         </is>
       </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Arts, Psychology and Theology</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arts; Psychology; Theology</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/news/faculties-at-abo-akademi-university-from-january-1-2025/</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university announcement of faculty structure.</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Social Sciences, Business and Economics, and Law</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Social sciences; Business; Economics; Law</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/news/faculties-at-abo-akademi-university-from-january-1-2025/</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university announcement of faculty structure.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science and Engineering</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Science; Engineering; IT</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/news/faculties-at-abo-akademi-university-from-january-1-2025/</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university announcement of faculty structure.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Education and Welfare Studies</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vaasa</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Education; Welfare studies</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/news/faculties-at-abo-akademi-university-from-january-1-2025/</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official university announcement of faculty structure.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Business and Economics</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Social Sciences, Business and Economics, and Law</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Business; Economics</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/about-abo-akademi-university/organisation/faculty-of-social-sciences-business-and-economics-and-law/department-of-business-and-economics/</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official department page.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Law</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Social Sciences, Business and Economics, and Law</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Law</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/news/faculties-at-abo-akademi-university-from-january-1-2025/</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department listed in official faculty announcement.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Computer Science</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Science and Engineering</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turku</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer science</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/subject/computer-science/</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department or subject page used as official academic unit reference.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">university_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">department_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">professor_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">title</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">research_areas</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">researchgate_url</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">google_scholar_url</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citation_count</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">h_index</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citation_source</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">citation_last_checked</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">official_profile_url</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">email</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">notes</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">last_verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aalto University</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Information and Communications Engineering</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Antti Oulasvirta</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Human-computer interaction; User interfaces; Human factors; Interactive AI; Computational modeling</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14763</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">63</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Research.com profile summary</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.aalto.fi/en/people/antti-oulasvirta</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">antti.oulasvirta@aalto.fi</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aalto official profile does not expose ResearchGate or Google Scholar links directly on the page snapshot used here.</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aalto University</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Computer Science</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samuel Kaski</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artificial intelligence; Machine learning; Probabilistic modeling; Computational health</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aalto official profile</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.aalto.fi/en/people/samuel-kaski</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official Aalto profile used for department and research-focus mapping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aalto University</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Computer Science</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aristides Gionis</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data mining; Algorithms; Network analysis; Machine learning</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aalto official profile</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.aalto.fi/en/people/aristides-gionis</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official Aalto profile used for department and research-focus mapping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Computer Science</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jukka K Nurminen</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor of Computer Science</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Efficient software systems; Energy-efficient software; Mobile peer-to-peer systems; Cloud solutions</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://scholar.google.fi/citations?user=cmftgn4AAAAJ</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki research portal profile text</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://researchportal.helsinki.fi/en/persons/jukka-k-nurminen/</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jukka.k.nurminen@helsinki.fi</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Google Scholar link is published directly on the university research portal profile.</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Computer Science</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mikko Koivisto</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Algorithms; Probabilistic inference; Artificial intelligence; Combinatorics</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki official profile</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/people/mikko-koivisto</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official University of Helsinki profile used for title and research areas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Computer Science</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hannu Toivonen</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artificial intelligence; Data science; Computational creativity; Data mining</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28000+</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60+</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Helsinki research group page</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.helsinki.fi/en/researchgroups/computational-creativity-and-data-mining/people/hannu-toivonen</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Citation count and h-index are stated on the official research group page as Google Scholar-based approximations.</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Research Centre of Gameful Realities</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Juho Hamari</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor of Gamification</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gamification; Game-based learning; Motivational systems; Extended reality; HCI</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.researchgate.net/profile/Juho-Hamari</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://scholar.google.com/citations?user=tKMlAegAAAAJ</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">50000+</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere University research centre page; ResearchGate profile</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://research.tuni.fi/gameful-realities/gamification-group/</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">juho.hamari@tuni.fi</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tampere research centre page states 50000+ citations and links both Google Scholar and ResearchGate.</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information Systems Science</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Jukka Heikkila</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information systems governance; Enterprise architecture; Business modelling</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.researchgate.net/profile/Jukka-Heikkilae</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://scholar.google.fi/citations?hl=en&amp;user=iLLaVWEAAAAJ&amp;view_op=list_works&amp;sortby=pubdate</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku staff profile</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/people/jukka-heikkila</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">jups@utu.fi</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku profile publishes direct Google Scholar and ResearchGate links in profile text.</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Health Technology</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Antti Airola</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Associate Professor</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artificial intelligence; Data analytics; Machine learning; Health technology</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100+</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Turku staff profile biography</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.utu.fi/en/people/antti-airola</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ajairo@utu.fi</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The official profile states that he has co-authored over 100 peer-reviewed articles and links Google Scholar and ResearchGate profiles from the page.</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Information Technology and Electrical Engineering</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Harri Oinas-Kukkonen</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor and Dean</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information systems science; Computer-human interaction; Persuasive design; Digital interventions</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.researchgate.net/profile/Harri_Oinas-Kukkonen</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://scholar.google.fi/citations?hl=en&amp;oi=ao&amp;user=CBDr26wAAAAJ</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu researcher profile</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/researchers/harri-oinas-kukkonen</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">harri.oinas-kukkonen@oulu.fi</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu profile exposes both Google Scholar and ResearchGate links directly.</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Biomimetics and Intelligent Systems Group</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heli Koskimaki</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adj. Prof.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machine learning; Data mining; Sensor fusion; Streaming data analysis; Wearable ICT</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Oulu researcher profile</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.oulu.fi/en/researchers/heli-koskimaki</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heli.koskimaki@oulu.fi</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official profile confirms both Google Scholar and ResearchGate profile links but their exact public URLs were not fetched automatically here.</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT University</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Engineering Science</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heikki Kalviainen</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer vision; Pattern recognition; Machine learning; AI engineering</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT official profile</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.lut.fi/en/profiles/heikki-kalviainen</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT official profile was used for role and research focus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT University</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Engineering Science</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lasse Lensu</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer vision; Pattern recognition; Image analysis; Machine learning</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT official profile</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.lut.fi/en/profiles/lasse-lensu</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT official profile was used for role and research focus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT University</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Engineering Science</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zhisong Liu</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Associate Professor</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Industrial AI; Machine learning; Computer vision; Autonomous systems</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13235</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LUT official profile</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.lut.fi/en/profiles/zhisong-liu</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official LUT profile states 13235 citations and h-index 48.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Computing</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pauli Miettinen</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data mining; Machine learning; Discrete optimization; Pattern discovery</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UEF official profile</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/person/pauli.miettinen</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UEF official profile used for role and research fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Computing</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Markku Tukiainen</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Human-computer interaction; Learning technologies; Computer science education</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UEF official profile</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/person/markku.tukiainen</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UEF official profile used for role and research fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Computing</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ville Hautamaki</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Speech processing; Speaker recognition; Biometrics; Audio analysis</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UEF official profile</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/person/ville.hautamaki</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UEF official profile used for role and research fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Eastern Finland</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Computing</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pasi Franti</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Machine learning; Pattern recognition; Data mining; Time series</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UEF official profile</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uef.fi/en/person/pasi.franti</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official UEF profile used for title and research-focus mapping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Information Technology</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Michael Emmerich</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Multi-objective optimization; Bayesian optimization; Data science; Simulation</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JYU official profile</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/people/michael-emmerich</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JYU official profile used for title and research topics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Jyvaskyla</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Faculty of Information Technology</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vagan Terziyan</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artificial intelligence; Semantic web; Knowledge engineering; Trust systems</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JYU official profile</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.jyu.fi/en/people/vagan-terziyan</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JYU official profile used for title and research topics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Technology and Innovations</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tero Vartiainen</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Information systems; Digital transformation; Human-computer interaction; Organizational communication</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa official profile</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/person/tero-vartiainen</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa official profile used for title and research description.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">School of Management</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Harri Jalonen</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Knowledge management; Artificial intelligence in organizations; Social robotics; Futures studies</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa official profile</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.uwasa.fi/en/person/harri-jalonen</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">University of Vaasa official profile used for title and research description.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t xml:space="preserve">Department of Management and Organisation</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Denise Salin</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Management and organisation; Workplace bullying; Leadership; Gender and diversity</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4296</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">31</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken official profile</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/person/denise-salin</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official Hanken profile states citation and h-index figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Marketing</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kaj Storbacka</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Markets and strategy; Sales management; Business model innovation; Customer relationships</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken official profile</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/person/kaj-storbacka</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken official profile used for title and research focus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken School of Economics</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Department of Economics</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joacim Tag</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Assistant Professor</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Economics; Applied econometrics; Productivity; Labor markets</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">750</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hanken official profile</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.hanken.fi/en/person/joacim-tag</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Official Hanken profile states citation and h-index figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t xml:space="preserve">Computer Science</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ivan Porres</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Professor</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Software engineering; Distributed systems; Formal methods; Process modeling</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi official profile</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://www.abo.fi/en/people/ivan-porres/</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi official profile used for title and research focus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abo Akademi University</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Computer Science</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t xml:space="preserve">Johan Lilius</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t xml:space="preserve">Professor</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t xml:space="preserve">Embedded systems; Dependable systems; Software engineering; Computer architecture</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t xml:space="preserve">Abo Akademi official profile</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-03-14</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-03-14</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
         <is>
           <t xml:space="preserve">https://www.abo.fi/en/people/johan-lilius/</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
+      <c r="M28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
         <is>
           <t xml:space="preserve">Abo Akademi official profile used for title and research focus.</t>
         </is>
